--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487846_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487846_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5478</v>
+        <v>4.3688</v>
       </c>
       <c r="E2" t="n">
-        <v>1.328</v>
+        <v>1.738</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2198</v>
+        <v>2.6308</v>
       </c>
       <c r="G2" t="n">
         <v>3.6652</v>
@@ -610,13 +610,13 @@
         <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5743</v>
+        <v>-0.7532</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.4786</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6856</v>
+        <v>-0.2746</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4557</v>
+        <v>1.9643</v>
       </c>
       <c r="E3" t="n">
-        <v>0.501</v>
+        <v>1.9407</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9546</v>
+        <v>0.0237</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7445000000000001</v>
+        <v>1.131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6546999999999999</v>
+        <v>-0.5884</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0898</v>
+        <v>1.7194</v>
       </c>
       <c r="J3" t="n">
-        <v>0.61</v>
+        <v>1.964</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6672</v>
+        <v>0.71</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0572</v>
+        <v>1.254</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1345</v>
+        <v>-0.8329</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0124</v>
+        <v>-1.2983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.147</v>
+        <v>0.4654</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9005</v>
+        <v>-0.2073</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9316</v>
+        <v>-0.0233</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9689</v>
+        <v>-0.184</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5799</v>
+        <v>1.1874</v>
       </c>
       <c r="E4" t="n">
-        <v>1.703</v>
+        <v>-0.3562</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1231</v>
+        <v>1.5436</v>
       </c>
       <c r="G4" t="n">
-        <v>1.131</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5884</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7194</v>
+        <v>0.0898</v>
       </c>
       <c r="J4" t="n">
-        <v>1.964</v>
+        <v>0.61</v>
       </c>
       <c r="K4" t="n">
-        <v>0.71</v>
+        <v>0.6672</v>
       </c>
       <c r="L4" t="n">
-        <v>1.254</v>
+        <v>-0.0572</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8329</v>
+        <v>0.1345</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2983</v>
+        <v>-0.0124</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4654</v>
+        <v>0.147</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5917</v>
+        <v>0.6322</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.261</v>
+        <v>0.0743</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3308</v>
+        <v>0.5579</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0016</v>
+        <v>0.1823</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0679</v>
+        <v>-1.109</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.06950000000000001</v>
+        <v>1.2913</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3693</v>
+        <v>1.6633</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0468</v>
+        <v>1.6886</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3225</v>
+        <v>-0.0253</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4347</v>
+        <v>2.4188</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4347</v>
+        <v>2.8074</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.3886</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0654</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3879</v>
+        <v>-1.1189</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3225</v>
+        <v>0.3633</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6244</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>2.4974</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0672</v>
+        <v>-0.6297</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3262</v>
+        <v>-0.7629</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3934</v>
+        <v>0.1332</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8137</v>
+        <v>0.8137</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8137</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7296</v>
+        <v>-0.2364</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7566</v>
+        <v>0.0679</v>
       </c>
       <c r="F6" t="n">
-        <v>1.027</v>
+        <v>-0.3043</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6633</v>
+        <v>1.3693</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6886</v>
+        <v>1.0468</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0253</v>
+        <v>0.3225</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4188</v>
+        <v>1.4347</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8074</v>
+        <v>1.4347</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3886</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.0654</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1189</v>
+        <v>-0.3879</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3633</v>
+        <v>0.3225</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6649</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4974</v>
+        <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5416</v>
+        <v>-0.1677</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4106</v>
+        <v>-0.3262</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1311</v>
+        <v>0.1586</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8137</v>
+        <v>-0.8137</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5838</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0998</v>
+        <v>-0.6398</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.357</v>
+        <v>-1.1612</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2572</v>
+        <v>0.5214</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9621</v>
@@ -1000,13 +1000,13 @@
         <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.762</v>
+        <v>-0.3021</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6929</v>
+        <v>-0.4972</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.1951</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7544</v>
+        <v>-3.0934</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.4514</v>
+        <v>-1.6747</v>
       </c>
       <c r="F8" t="n">
-        <v>1.697</v>
+        <v>-1.4187</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6322</v>
+        <v>-1.0071</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7098</v>
+        <v>-0.6887</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0776</v>
+        <v>-0.3184</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3498</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6848</v>
+        <v>-0.3498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0694</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0168</v>
+        <v>-0.6573</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.025</v>
+        <v>-0.3389</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.3184</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5448</v>
+        <v>-0.4807</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0472</v>
+        <v>-0.2843</v>
       </c>
       <c r="U8" t="n">
-        <v>1.592</v>
+        <v>-0.1964</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8751</v>
+        <v>-1.3975</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5561</v>
+        <v>-3.494</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1081</v>
+        <v>-4.3395</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.448</v>
+        <v>0.8455</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0071</v>
+        <v>-1.6322</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6887</v>
+        <v>-1.7098</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3184</v>
+        <v>0.0776</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3498</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3498</v>
+        <v>-0.6848</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0694</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6573</v>
+        <v>-1.0168</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3389</v>
+        <v>-1.025</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3184</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2081</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9434</v>
+        <v>-0.1947</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7177</v>
+        <v>-0.9353</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2257</v>
+        <v>0.7406</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3975</v>
+        <v>-1.8751</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6462</v>
+        <v>-3.8126</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.5439</v>
+        <v>-6.0919</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8976</v>
+        <v>2.2793</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9712</v>
@@ -1234,13 +1234,13 @@
         <v>2.7055</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3857</v>
+        <v>-0.5521</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1496</v>
+        <v>-0.6976</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2361</v>
+        <v>0.1456</v>
       </c>
       <c r="V10" t="n">
         <v>1.1675</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.204299999999998</v>
+        <v>-3.573400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.6171</v>
+        <v>-10.9859</v>
       </c>
       <c r="F11" t="n">
         <v>7.4126</v>
@@ -1279,7 +1279,7 @@
         <v>2.0007</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8783</v>
+        <v>2.878300000000001</v>
       </c>
       <c r="I11" t="n">
         <v>-0.8776000000000002</v>
@@ -1288,7 +1288,7 @@
         <v>5.656000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2889</v>
+        <v>7.288899999999999</v>
       </c>
       <c r="L11" t="n">
         <v>-1.6329</v>
@@ -1297,7 +1297,7 @@
         <v>-3.6553</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.410600000000001</v>
+        <v>-4.4106</v>
       </c>
       <c r="O11" t="n">
         <v>0.7553999999999998</v>
@@ -1312,13 +1312,13 @@
         <v>14.5682</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.2862</v>
+        <v>-2.6553</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.562199999999999</v>
+        <v>-3.9311</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2759</v>
+        <v>1.276</v>
       </c>
       <c r="V11" t="n">
         <v>-2.9188</v>
@@ -1327,7 +1327,7 @@
         <v>1.8574</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.7762</v>
+        <v>-4.776199999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8798</v>
+        <v>4.887</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4014</v>
+        <v>1.6513</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4784</v>
+        <v>3.2357</v>
       </c>
       <c r="G12" t="n">
         <v>1.3464</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5366</v>
+        <v>1.5437</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8506</v>
+        <v>0.1006</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6859</v>
+        <v>1.4432</v>
       </c>
       <c r="V12" t="n">
         <v>0.1238</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0487</v>
+        <v>4.675</v>
       </c>
       <c r="E13" t="n">
-        <v>1.436</v>
+        <v>1.8646</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6127</v>
+        <v>2.8104</v>
       </c>
       <c r="G13" t="n">
         <v>2.5665</v>
@@ -1468,13 +1468,13 @@
         <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2264</v>
+        <v>0.3999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7705</v>
+        <v>-0.3419</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5442</v>
+        <v>0.7418</v>
       </c>
       <c r="V13" t="n">
         <v>0.4599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3108</v>
+        <v>2.4727</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8159</v>
+        <v>-0.7088</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1267</v>
+        <v>3.1815</v>
       </c>
       <c r="G14" t="n">
         <v>1.075</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9819</v>
+        <v>1.1438</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3047</v>
+        <v>-0.1976</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2866</v>
+        <v>1.3414</v>
       </c>
       <c r="V14" t="n">
         <v>2.3351</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2195</v>
+        <v>2.2258</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1387</v>
+        <v>0.0315</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0808</v>
+        <v>2.1943</v>
       </c>
       <c r="G15" t="n">
         <v>0.5617</v>
@@ -1624,13 +1624,13 @@
         <v>2.4974</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2009</v>
+        <v>0.2073</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.199</v>
+        <v>-0.3062</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4</v>
+        <v>0.5135</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0547</v>
+        <v>0.4643</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5349</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4802</v>
+        <v>-0.3921</v>
       </c>
       <c r="G16" t="n">
         <v>0.2694</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2146</v>
+        <v>0.1949</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1305</v>
+        <v>0.191</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0842</v>
+        <v>0.0039</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6694</v>
+        <v>-0.3734</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1299</v>
+        <v>-2.8687</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4606</v>
+        <v>2.4953</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8501</v>
+        <v>-0.2303</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3923</v>
+        <v>-0.4263</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5422</v>
+        <v>0.1959</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2402</v>
+        <v>-0.618</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.5609</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0401</v>
+        <v>-0.0572</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0902</v>
+        <v>0.3877</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5924</v>
+        <v>0.1346</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5021</v>
+        <v>0.2531</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1807</v>
+        <v>0.5032</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1214</v>
+        <v>-0.1695</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3021</v>
+        <v>0.6727</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7701</v>
+        <v>-0.5162</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5345</v>
+        <v>-1.2371</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7644</v>
+        <v>0.7209</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2125</v>
+        <v>-0.8501</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1086</v>
+        <v>-2.3923</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1038</v>
+        <v>1.5422</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3512</v>
+        <v>0.2402</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0384</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3896</v>
+        <v>1.0401</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1387</v>
+        <v>-1.0902</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.147</v>
+        <v>-1.5924</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2857</v>
+        <v>0.5021</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2342</v>
+        <v>0.3339</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1833</v>
+        <v>-0.2286</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4176</v>
+        <v>0.5624</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4885</v>
+        <v>-0.7217</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4045</v>
+        <v>-1.4274</v>
       </c>
       <c r="F19" t="n">
-        <v>1.916</v>
+        <v>0.7057</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2303</v>
+        <v>-1.2125</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4263</v>
+        <v>-0.1086</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1959</v>
+        <v>-1.1038</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.618</v>
+        <v>-1.3512</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5609</v>
+        <v>0.0384</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0572</v>
+        <v>-1.3896</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3877</v>
+        <v>0.1387</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1346</v>
+        <v>-0.147</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2531</v>
+        <v>0.2857</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.612</v>
+        <v>0.2827</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7053</v>
+        <v>-0.0762</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.3588</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8296</v>
+        <v>-1.2844</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.527</v>
+        <v>-1.7196</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3025</v>
+        <v>0.4352</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4399</v>
+        <v>-1.5073</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2391</v>
+        <v>-1.2493</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2008</v>
+        <v>-0.258</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.672</v>
+        <v>-1.1927</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7896</v>
+        <v>-0.4693</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1176</v>
+        <v>-0.7234</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7679</v>
+        <v>-0.3146</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4495</v>
+        <v>-0.78</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3184</v>
+        <v>0.4654</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0812</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>1.524</v>
+        <v>0.8255</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3073</v>
+        <v>-0.0919</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2166</v>
+        <v>0.9173</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9337</v>
+        <v>-2.5591</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2553</v>
+        <v>-1.2564</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3217</v>
+        <v>-1.3027</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5073</v>
+        <v>-1.5795</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2493</v>
+        <v>-1.3305</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.258</v>
+        <v>-0.249</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1927</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4693</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7234</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3146</v>
+        <v>-0.9227</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.78</v>
+        <v>-0.6737</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4654</v>
+        <v>-0.249</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1762</v>
+        <v>-0.4365</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6277</v>
+        <v>-0.3915</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8038</v>
+        <v>-0.045</v>
       </c>
       <c r="V21" t="n">
-        <v>0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6178</v>
+        <v>-2.6369</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2564</v>
+        <v>-2.5986</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3615</v>
+        <v>-0.0383</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5795</v>
+        <v>-2.4399</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3305</v>
+        <v>-2.2391</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.249</v>
+        <v>-0.2008</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.672</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.7896</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9227</v>
+        <v>-1.7679</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6737</v>
+        <v>-1.4495</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.249</v>
+        <v>-0.3184</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6244</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4952</v>
+        <v>0.7166</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3915</v>
+        <v>0.2358</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1037</v>
+        <v>0.4809</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1675</v>
+        <v>1.1675</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.204400000000001</v>
+        <v>6.6331</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4125</v>
+        <v>-7.412799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>12.6171</v>
+        <v>14.0459</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0006</v>
@@ -2221,25 +2221,25 @@
         <v>0.8774999999999996</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6554</v>
+        <v>3.655399999999999</v>
       </c>
       <c r="K23" t="n">
         <v>4.4108</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7554999999999997</v>
+        <v>-0.7554999999999998</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.656</v>
+        <v>-5.656000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.288900000000001</v>
+        <v>-7.2889</v>
       </c>
       <c r="O23" t="n">
         <v>1.633</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.5683</v>
@@ -2248,19 +2248,19 @@
         <v>14.5682</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2863</v>
+        <v>5.715</v>
       </c>
       <c r="T23" t="n">
         <v>-1.276</v>
       </c>
       <c r="U23" t="n">
-        <v>5.5622</v>
+        <v>6.990899999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>2.918800000000001</v>
+        <v>2.9188</v>
       </c>
       <c r="W23" t="n">
-        <v>4.7762</v>
+        <v>4.776199999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-1.8575</v>
